--- a/SuppXLS/Scen_z_MACC-TRA-CAP-WEM.xlsx
+++ b/SuppXLS/Scen_z_MACC-TRA-CAP-WEM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6B07D-A28D-44C6-9F3F-4A59DE7D6598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AB1171-D66A-43B5-8110-B5CBECA028EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="114">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -363,19 +363,27 @@
     <t>District Heating (Commercial)</t>
   </si>
   <si>
-    <t>WAM</t>
-  </si>
-  <si>
     <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>WAM NEP25</t>
+  </si>
+  <si>
+    <t>For projected years we have provided here the number of dwellings that undertake energy efficiency measures that bring the dwelling from a BER worse than B2 to one of B2 or better, excluding solar PV. This may not align exactly with the wording of the CAP target  of "B2 cost optimal or carbon equivalent". For 2024 we include an estimate of the cumulative number of dwellings that have undergone upgrade works  from 2018-2024 that improved their BER rating to B2 or better through SEAI schemes or Local Authority schemes, excluding solar PV only upgrades.</t>
+  </si>
+  <si>
+    <t>Assume that this item is for HP retrofits, excluding HP installed in new dwellings. The figure given for 2024 is the total number of HPs installed through SEAI and Local Authority retrofit schemes for 2019-2024.</t>
+  </si>
+  <si>
+    <t>Assume includes public services</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -784,12 +792,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -800,8 +802,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1008,8 +1016,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="44">
+  <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -1054,8 +1077,9 @@
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="2" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1084,7 +1108,8 @@
     <xf numFmtId="2" fontId="25" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1093,8 +1118,6 @@
     <xf numFmtId="0" fontId="0" fillId="39" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1102,9 +1125,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1113,21 +1133,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="39" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="40" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="44">
+  <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="25" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="29" builtinId="38" customBuiltin="1"/>
@@ -1172,6 +1196,7 @@
     <cellStyle name="Title" xfId="3" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="19" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="16" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Worksheet Title" xfId="44" xr:uid="{2CACBA1F-A575-42FA-927A-0A5611CAB8B7}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1546,7 +1571,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>8</v>
@@ -1657,27 +1682,63 @@
       </c>
       <c r="P6">
         <f>M22/1000</f>
-        <v>147.352</v>
+        <v>131.80653391912145</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:AN6" si="0">N22/1000</f>
-        <v>193.19900000000001</v>
+        <f t="shared" ref="Q6:AD6" si="0">N22/1000</f>
+        <v>168.37462820670515</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>239.04599999999999</v>
+        <v>212.76994018992548</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>284.89299999999997</v>
+        <v>266.25376204901852</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>330.74</v>
-      </c>
-      <c r="AN6">
+        <v>330.73976204901851</v>
+      </c>
+      <c r="U6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>402.89463103844196</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>483.2703858623878</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>572.76939329977881</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>671.36476917221398</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>803.01176917221392</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>934.12303147115836</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>1062.6675992603252</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="0"/>
+        <v>1188.7572164680005</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="0"/>
+        <v>1327.9586222564651</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="0"/>
+        <v>1470.1261569172073</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
@@ -1699,7 +1760,46 @@
       <c r="P7">
         <v>0</v>
       </c>
-      <c r="AN7">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
         <v>0</v>
       </c>
     </row>
@@ -1721,26 +1821,63 @@
       </c>
       <c r="P8">
         <f>M23/1000</f>
-        <v>126.626</v>
+        <v>115.25945447616215</v>
       </c>
       <c r="Q8">
-        <f t="shared" ref="Q8:T8" si="1">N23/1000</f>
-        <v>164.822</v>
+        <f t="shared" ref="Q8:AD8" si="1">N23/1000</f>
+        <v>146.80932931771784</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>203.018</v>
+        <v>183.96444466028123</v>
       </c>
       <c r="S8">
         <f t="shared" si="1"/>
-        <v>241.214</v>
+        <v>227.78337094489672</v>
       </c>
       <c r="T8">
         <f t="shared" si="1"/>
-        <v>279.41000000000003</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
+        <v>279.4113709448967</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="1"/>
+        <v>332.26419836038559</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="1"/>
+        <v>387.04905666471603</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="1"/>
+        <v>443.15132676393108</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="1"/>
+        <v>501.36482754287874</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="1"/>
+        <v>533.24282754287867</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>553.52832832182628</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="1"/>
+        <v>569.77954423927815</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="1"/>
+        <v>578.05204909329859</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="1"/>
+        <v>577.46283565678266</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="1"/>
+        <v>570.36307433789364</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
@@ -1761,23 +1898,63 @@
       </c>
       <c r="P9">
         <f>M26/1000</f>
-        <v>8.7680000000000007</v>
+        <v>8.9171428571428564</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q9:T9" si="2">N26/1000</f>
-        <v>12.726000000000001</v>
+        <f t="shared" ref="Q9:AD9" si="2">N26/1000</f>
+        <v>12.837857142857143</v>
       </c>
       <c r="R9">
         <f t="shared" si="2"/>
-        <v>16.684000000000001</v>
+        <v>16.758571428571429</v>
       </c>
       <c r="S9">
         <f t="shared" si="2"/>
-        <v>20.641999999999999</v>
+        <v>20.679285714285715</v>
       </c>
       <c r="T9">
         <f t="shared" si="2"/>
         <v>24.6</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="2"/>
+        <v>29.09</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="2"/>
+        <v>33.58</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="2"/>
+        <v>38.07</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="2"/>
+        <v>42.56</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="2"/>
+        <v>47.05</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="2"/>
+        <v>69.184874566279916</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="2"/>
+        <v>91.319749132559835</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="2"/>
+        <v>113.45462369883975</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="2"/>
+        <v>135.58949826511969</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="2"/>
+        <v>157.72437283139962</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
@@ -1800,7 +1977,60 @@
         <f>0/1000</f>
         <v>0</v>
       </c>
+      <c r="Q10">
+        <f t="shared" ref="Q10:AD11" si="3">0/1000</f>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="U10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1824,7 +2054,60 @@
         <f>0/1000</f>
         <v>0</v>
       </c>
+      <c r="Q11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="U11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1846,25 +2129,64 @@
       </c>
       <c r="P12">
         <f>M24/1000</f>
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="Q12" s="16">
-        <f t="shared" ref="Q12:T12" si="3">N24/1000</f>
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="R12" s="16">
-        <f t="shared" si="3"/>
-        <v>0.99</v>
-      </c>
-      <c r="S12" s="16">
-        <f t="shared" si="3"/>
-        <v>1.167</v>
-      </c>
-      <c r="T12" s="16">
-        <f t="shared" si="3"/>
-        <v>1.3440000000000001</v>
-      </c>
-      <c r="U12" s="16"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q12:AD12" si="4">N24/1000</f>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="4"/>
+        <v>0.28199999999999997</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -1885,732 +2207,1007 @@
       <c r="P13">
         <v>0</v>
       </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
         <v>0</v>
       </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C21" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="43" t="s">
+    <row r="21" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B21" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="34"/>
+      <c r="D21" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="18">
         <v>2018</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <v>2019</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <v>2020</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <v>2021</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <v>2022</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="18">
         <v>2023</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <v>2024</v>
       </c>
-      <c r="L21" s="44">
+      <c r="L21" s="33">
         <v>2025</v>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="18">
         <v>2026</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <v>2027</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="18">
         <v>2028</v>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="18">
         <v>2029</v>
       </c>
-      <c r="Q21" s="44">
+      <c r="Q21" s="33">
         <v>2030</v>
       </c>
-      <c r="R21" s="17">
+      <c r="R21" s="18">
         <v>2031</v>
       </c>
-      <c r="S21" s="17">
+      <c r="S21" s="18">
         <v>2032</v>
       </c>
-      <c r="T21" s="17">
+      <c r="T21" s="18">
         <v>2033</v>
       </c>
-      <c r="U21" s="17">
+      <c r="U21" s="18">
         <v>2034</v>
       </c>
-      <c r="V21" s="17">
+      <c r="V21" s="18">
         <v>2035</v>
       </c>
-      <c r="W21" s="17">
+      <c r="W21" s="18">
         <v>2036</v>
       </c>
-      <c r="X21" s="17">
+      <c r="X21" s="18">
         <v>2037</v>
       </c>
-      <c r="Y21" s="17">
+      <c r="Y21" s="18">
         <v>2038</v>
       </c>
-      <c r="Z21" s="17">
+      <c r="Z21" s="18">
         <v>2039</v>
       </c>
-      <c r="AA21" s="44">
+      <c r="AA21" s="33">
         <v>2040</v>
       </c>
-      <c r="AB21" s="17">
+      <c r="AB21" s="18">
         <v>2041</v>
       </c>
-      <c r="AC21" s="17">
+      <c r="AC21" s="18">
         <v>2042</v>
       </c>
-      <c r="AD21" s="17">
+      <c r="AD21" s="18">
         <v>2043</v>
       </c>
-      <c r="AE21" s="17">
+      <c r="AE21" s="18">
         <v>2044</v>
       </c>
-      <c r="AF21" s="17">
+      <c r="AF21" s="18">
         <v>2045</v>
       </c>
-      <c r="AG21" s="17">
+      <c r="AG21" s="18">
         <v>2046</v>
       </c>
-      <c r="AH21" s="17">
+      <c r="AH21" s="18">
         <v>2047</v>
       </c>
-      <c r="AI21" s="17">
+      <c r="AI21" s="18">
         <v>2048</v>
       </c>
-      <c r="AJ21" s="17">
+      <c r="AJ21" s="18">
         <v>2049</v>
       </c>
-      <c r="AK21" s="44">
+      <c r="AK21" s="33">
         <v>2050</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C22" s="19" t="s">
+    <row r="22" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B22" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="21">
-        <v>101505</v>
-      </c>
-      <c r="M22" s="22">
-        <v>147352</v>
-      </c>
-      <c r="N22" s="22">
-        <v>193199</v>
-      </c>
-      <c r="O22" s="22">
-        <v>239046</v>
-      </c>
-      <c r="P22" s="22">
-        <v>284893</v>
-      </c>
-      <c r="Q22" s="21">
-        <v>330740</v>
-      </c>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="19"/>
-      <c r="AG22" s="19"/>
-      <c r="AH22" s="19"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="20"/>
+      <c r="E22" s="35">
+        <v>4528</v>
+      </c>
+      <c r="F22" s="35">
+        <v>8473</v>
+      </c>
+      <c r="G22" s="35">
+        <v>12576</v>
+      </c>
+      <c r="H22" s="35">
+        <v>21085</v>
+      </c>
+      <c r="I22" s="35">
+        <v>36002</v>
+      </c>
+      <c r="J22" s="35">
+        <v>57730</v>
+      </c>
+      <c r="K22" s="35">
+        <v>76458.133004706353</v>
+      </c>
+      <c r="L22" s="35">
+        <v>101504.59834396423</v>
+      </c>
+      <c r="M22" s="35">
+        <v>131806.53391912146</v>
+      </c>
+      <c r="N22" s="35">
+        <v>168374.62820670515</v>
+      </c>
+      <c r="O22" s="35">
+        <v>212769.94018992549</v>
+      </c>
+      <c r="P22" s="35">
+        <v>266253.76204901852</v>
+      </c>
+      <c r="Q22" s="35">
+        <v>330739.76204901852</v>
+      </c>
+      <c r="R22" s="35">
+        <v>402894.63103844196</v>
+      </c>
+      <c r="S22" s="35">
+        <v>483270.38586238777</v>
+      </c>
+      <c r="T22" s="35">
+        <v>572769.39329977881</v>
+      </c>
+      <c r="U22" s="35">
+        <v>671364.76917221397</v>
+      </c>
+      <c r="V22" s="35">
+        <v>803011.76917221397</v>
+      </c>
+      <c r="W22" s="35">
+        <v>934123.03147115838</v>
+      </c>
+      <c r="X22" s="35">
+        <v>1062667.5992603253</v>
+      </c>
+      <c r="Y22" s="35">
+        <v>1188757.2164680006</v>
+      </c>
+      <c r="Z22" s="35">
+        <v>1327958.622256465</v>
+      </c>
+      <c r="AA22" s="35">
+        <v>1470126.1569172072</v>
+      </c>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="20"/>
+      <c r="AH22" s="20"/>
+      <c r="AI22" s="20"/>
+      <c r="AJ22" s="20"/>
+      <c r="AK22" s="21"/>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C23" s="19" t="s">
+    <row r="23" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="21">
-        <v>88430</v>
-      </c>
-      <c r="M23" s="22">
-        <v>126626</v>
-      </c>
-      <c r="N23" s="22">
-        <v>164822</v>
-      </c>
-      <c r="O23" s="22">
-        <v>203018</v>
-      </c>
-      <c r="P23" s="22">
-        <v>241214</v>
-      </c>
-      <c r="Q23" s="21">
-        <v>279410</v>
-      </c>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="19"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="19"/>
-      <c r="AK23" s="20"/>
+      <c r="E23" s="35">
+        <v>2791</v>
+      </c>
+      <c r="F23" s="35">
+        <v>6306</v>
+      </c>
+      <c r="G23" s="35">
+        <v>12228</v>
+      </c>
+      <c r="H23" s="35">
+        <v>23671</v>
+      </c>
+      <c r="I23" s="35">
+        <v>33157</v>
+      </c>
+      <c r="J23" s="35">
+        <v>46227</v>
+      </c>
+      <c r="K23" s="35">
+        <v>65580.100332647708</v>
+      </c>
+      <c r="L23" s="35">
+        <v>88429.861651536645</v>
+      </c>
+      <c r="M23" s="35">
+        <v>115259.45447616215</v>
+      </c>
+      <c r="N23" s="35">
+        <v>146809.32931771784</v>
+      </c>
+      <c r="O23" s="35">
+        <v>183964.44466028124</v>
+      </c>
+      <c r="P23" s="35">
+        <v>227783.37094489671</v>
+      </c>
+      <c r="Q23" s="35">
+        <v>279411.37094489671</v>
+      </c>
+      <c r="R23" s="35">
+        <v>332264.19836038561</v>
+      </c>
+      <c r="S23" s="35">
+        <v>387049.05666471604</v>
+      </c>
+      <c r="T23" s="35">
+        <v>443151.32676393108</v>
+      </c>
+      <c r="U23" s="35">
+        <v>501364.82754287875</v>
+      </c>
+      <c r="V23" s="35">
+        <v>533242.82754287869</v>
+      </c>
+      <c r="W23" s="35">
+        <v>553528.32832182629</v>
+      </c>
+      <c r="X23" s="35">
+        <v>569779.54423927818</v>
+      </c>
+      <c r="Y23" s="35">
+        <v>578052.04909329861</v>
+      </c>
+      <c r="Z23" s="35">
+        <v>577462.83565678261</v>
+      </c>
+      <c r="AA23" s="35">
+        <v>570363.07433789363</v>
+      </c>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
+      <c r="AG23" s="20"/>
+      <c r="AH23" s="20"/>
+      <c r="AI23" s="20"/>
+      <c r="AJ23" s="20"/>
+      <c r="AK23" s="21"/>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C24" s="19" t="s">
+    <row r="24" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="16"/>
+      <c r="D24" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
       <c r="J24" s="23">
         <v>61</v>
       </c>
       <c r="K24" s="23">
         <v>282</v>
       </c>
-      <c r="L24" s="22">
-        <v>459</v>
-      </c>
-      <c r="M24" s="22">
-        <v>636</v>
-      </c>
-      <c r="N24" s="22">
-        <v>813</v>
-      </c>
-      <c r="O24" s="22">
-        <v>990</v>
-      </c>
-      <c r="P24" s="22">
-        <v>1167</v>
-      </c>
-      <c r="Q24" s="24">
-        <v>1344</v>
-      </c>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="19"/>
-      <c r="AG24" s="19"/>
-      <c r="AH24" s="19"/>
-      <c r="AI24" s="19"/>
-      <c r="AJ24" s="19"/>
-      <c r="AK24" s="20"/>
+      <c r="L24" s="35">
+        <v>282</v>
+      </c>
+      <c r="M24" s="35">
+        <v>282</v>
+      </c>
+      <c r="N24" s="35">
+        <v>282</v>
+      </c>
+      <c r="O24" s="35">
+        <v>282</v>
+      </c>
+      <c r="P24" s="35">
+        <v>282</v>
+      </c>
+      <c r="Q24" s="35">
+        <v>282</v>
+      </c>
+      <c r="R24" s="35">
+        <v>282</v>
+      </c>
+      <c r="S24" s="35">
+        <v>282</v>
+      </c>
+      <c r="T24" s="35">
+        <v>282</v>
+      </c>
+      <c r="U24" s="35">
+        <v>282</v>
+      </c>
+      <c r="V24" s="35">
+        <v>282</v>
+      </c>
+      <c r="W24" s="35">
+        <v>282</v>
+      </c>
+      <c r="X24" s="35">
+        <v>282</v>
+      </c>
+      <c r="Y24" s="35">
+        <v>282</v>
+      </c>
+      <c r="Z24" s="35">
+        <v>282</v>
+      </c>
+      <c r="AA24" s="35">
+        <v>282</v>
+      </c>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="20"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="20"/>
+      <c r="AJ24" s="20"/>
+      <c r="AK24" s="21"/>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C25" s="19" t="s">
+    <row r="25" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B25" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="21">
+      <c r="E25" s="35">
+        <v>10</v>
+      </c>
+      <c r="F25" s="35">
+        <v>57</v>
+      </c>
+      <c r="G25" s="35">
+        <v>103</v>
+      </c>
+      <c r="H25" s="35">
+        <v>208</v>
+      </c>
+      <c r="I25" s="35">
+        <v>379</v>
+      </c>
+      <c r="J25" s="35">
+        <v>675</v>
+      </c>
+      <c r="K25" s="35">
+        <v>937.5</v>
+      </c>
+      <c r="L25" s="35">
         <v>1200</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M25" s="35">
         <v>2160</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="35">
         <v>3120</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="35">
         <v>4080</v>
       </c>
-      <c r="P25" s="22">
+      <c r="P25" s="35">
         <v>5040</v>
       </c>
-      <c r="Q25" s="21">
+      <c r="Q25" s="35">
         <v>6000</v>
       </c>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="19"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="19"/>
-      <c r="AK25" s="20"/>
+      <c r="R25" s="35">
+        <v>7800</v>
+      </c>
+      <c r="S25" s="35">
+        <v>9600</v>
+      </c>
+      <c r="T25" s="35">
+        <v>11400</v>
+      </c>
+      <c r="U25" s="35">
+        <v>13200</v>
+      </c>
+      <c r="V25" s="35">
+        <v>15000</v>
+      </c>
+      <c r="W25" s="35">
+        <v>14000</v>
+      </c>
+      <c r="X25" s="35">
+        <v>13000</v>
+      </c>
+      <c r="Y25" s="35">
+        <v>12000</v>
+      </c>
+      <c r="Z25" s="35">
+        <v>11000</v>
+      </c>
+      <c r="AA25" s="35">
+        <v>10000</v>
+      </c>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="20"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="20"/>
+      <c r="AG25" s="20"/>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="20"/>
+      <c r="AJ25" s="20"/>
+      <c r="AK25" s="21"/>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C26" s="19" t="s">
+    <row r="26" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B26" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="20"/>
+      <c r="D26" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="21">
-        <v>4810</v>
-      </c>
-      <c r="M26" s="22">
-        <v>8768</v>
-      </c>
-      <c r="N26" s="22">
-        <v>12726</v>
-      </c>
-      <c r="O26" s="22">
-        <v>16684</v>
-      </c>
-      <c r="P26" s="22">
-        <v>20642</v>
-      </c>
-      <c r="Q26" s="21">
+      <c r="E26" s="20">
+        <v>167</v>
+      </c>
+      <c r="F26" s="20">
+        <v>454</v>
+      </c>
+      <c r="G26" s="20">
+        <v>878</v>
+      </c>
+      <c r="H26" s="20">
+        <v>1770</v>
+      </c>
+      <c r="I26" s="20">
+        <v>2135</v>
+      </c>
+      <c r="J26" s="20">
+        <v>2856</v>
+      </c>
+      <c r="K26" s="20">
+        <v>3926.2142857142858</v>
+      </c>
+      <c r="L26" s="20">
+        <v>4996.4285714285716</v>
+      </c>
+      <c r="M26" s="20">
+        <v>8917.1428571428569</v>
+      </c>
+      <c r="N26" s="20">
+        <v>12837.857142857143</v>
+      </c>
+      <c r="O26" s="20">
+        <v>16758.571428571428</v>
+      </c>
+      <c r="P26" s="20">
+        <v>20679.285714285714</v>
+      </c>
+      <c r="Q26" s="20">
         <v>24600</v>
       </c>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="19"/>
-      <c r="AC26" s="19"/>
-      <c r="AD26" s="19"/>
-      <c r="AE26" s="19"/>
-      <c r="AF26" s="19"/>
-      <c r="AG26" s="19"/>
-      <c r="AH26" s="19"/>
-      <c r="AI26" s="19"/>
-      <c r="AJ26" s="19"/>
-      <c r="AK26" s="20"/>
+      <c r="R26" s="20">
+        <v>29090</v>
+      </c>
+      <c r="S26" s="20">
+        <v>33580</v>
+      </c>
+      <c r="T26" s="20">
+        <v>38070</v>
+      </c>
+      <c r="U26" s="20">
+        <v>42560</v>
+      </c>
+      <c r="V26" s="20">
+        <v>47050</v>
+      </c>
+      <c r="W26" s="20">
+        <v>69184.874566279919</v>
+      </c>
+      <c r="X26" s="20">
+        <v>91319.749132559838</v>
+      </c>
+      <c r="Y26" s="20">
+        <v>113454.62369883976</v>
+      </c>
+      <c r="Z26" s="20">
+        <v>135589.49826511968</v>
+      </c>
+      <c r="AA26" s="20">
+        <v>157724.37283139961</v>
+      </c>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AD26" s="20"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="20"/>
+      <c r="AH26" s="20"/>
+      <c r="AI26" s="20"/>
+      <c r="AJ26" s="20"/>
+      <c r="AK26" s="21"/>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C27" s="25" t="s">
+    <row r="27" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B27" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="C27" s="36"/>
+      <c r="D27" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="28">
+      <c r="E27" s="35">
+        <v>167</v>
+      </c>
+      <c r="F27" s="35">
+        <v>454</v>
+      </c>
+      <c r="G27" s="35">
+        <v>878</v>
+      </c>
+      <c r="H27" s="35">
+        <v>1770</v>
+      </c>
+      <c r="I27" s="35">
+        <v>2135</v>
+      </c>
+      <c r="J27" s="35">
+        <v>2821</v>
+      </c>
+      <c r="K27" s="35">
+        <v>3810.5</v>
+      </c>
+      <c r="L27" s="35">
         <v>4800</v>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="35">
         <v>8640</v>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="35">
         <v>12480</v>
       </c>
-      <c r="O27" s="29">
+      <c r="O27" s="35">
         <v>16320</v>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="35">
         <v>20160</v>
       </c>
-      <c r="Q27" s="28">
+      <c r="Q27" s="35">
         <v>24000</v>
       </c>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="27"/>
-      <c r="AD27" s="27"/>
-      <c r="AE27" s="27"/>
-      <c r="AF27" s="27"/>
-      <c r="AG27" s="27"/>
-      <c r="AH27" s="27"/>
-      <c r="AI27" s="27"/>
-      <c r="AJ27" s="27"/>
-      <c r="AK27" s="31"/>
+      <c r="R27" s="35">
+        <v>28200</v>
+      </c>
+      <c r="S27" s="35">
+        <v>32400</v>
+      </c>
+      <c r="T27" s="35">
+        <v>36600</v>
+      </c>
+      <c r="U27" s="35">
+        <v>40800</v>
+      </c>
+      <c r="V27" s="35">
+        <v>45000</v>
+      </c>
+      <c r="W27" s="35">
+        <v>66844.874566279919</v>
+      </c>
+      <c r="X27" s="35">
+        <v>88689.749132559838</v>
+      </c>
+      <c r="Y27" s="35">
+        <v>110534.62369883976</v>
+      </c>
+      <c r="Z27" s="35">
+        <v>132379.49826511968</v>
+      </c>
+      <c r="AA27" s="35">
+        <v>154224.37283139961</v>
+      </c>
+      <c r="AB27" s="26"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="26"/>
+      <c r="AE27" s="26"/>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="26"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="26"/>
+      <c r="AJ27" s="26"/>
+      <c r="AK27" s="27"/>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C28" s="32" t="s">
+    <row r="28" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B28" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="E28" s="35">
+        <v>0</v>
+      </c>
+      <c r="F28" s="35">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35">
+        <v>0</v>
+      </c>
+      <c r="H28" s="35">
+        <v>0</v>
+      </c>
+      <c r="I28" s="35">
+        <v>0</v>
+      </c>
+      <c r="J28" s="35">
+        <v>35</v>
+      </c>
+      <c r="K28" s="35">
+        <v>115.71428571428571</v>
+      </c>
       <c r="L28" s="35">
-        <v>10</v>
-      </c>
-      <c r="M28" s="36">
-        <v>128</v>
-      </c>
-      <c r="N28" s="36">
-        <v>246</v>
-      </c>
-      <c r="O28" s="36">
-        <v>364</v>
-      </c>
-      <c r="P28" s="36">
-        <v>482</v>
+        <v>196.42857142857142</v>
+      </c>
+      <c r="M28" s="35">
+        <v>277.14285714285711</v>
+      </c>
+      <c r="N28" s="35">
+        <v>357.85714285714283</v>
+      </c>
+      <c r="O28" s="35">
+        <v>438.57142857142856</v>
+      </c>
+      <c r="P28" s="35">
+        <v>519.28571428571422</v>
       </c>
       <c r="Q28" s="35">
         <v>600</v>
       </c>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="34"/>
-      <c r="AC28" s="34"/>
-      <c r="AD28" s="34"/>
-      <c r="AE28" s="34"/>
-      <c r="AF28" s="34"/>
-      <c r="AG28" s="34"/>
-      <c r="AH28" s="34"/>
-      <c r="AI28" s="34"/>
-      <c r="AJ28" s="34"/>
-      <c r="AK28" s="38"/>
+      <c r="R28" s="35">
+        <v>890</v>
+      </c>
+      <c r="S28" s="35">
+        <v>1180</v>
+      </c>
+      <c r="T28" s="35">
+        <v>1470</v>
+      </c>
+      <c r="U28" s="35">
+        <v>1760</v>
+      </c>
+      <c r="V28" s="35">
+        <v>2050</v>
+      </c>
+      <c r="W28" s="35">
+        <v>2340</v>
+      </c>
+      <c r="X28" s="35">
+        <v>2630</v>
+      </c>
+      <c r="Y28" s="35">
+        <v>2920</v>
+      </c>
+      <c r="Z28" s="35">
+        <v>3210</v>
+      </c>
+      <c r="AA28" s="35">
+        <v>3500</v>
+      </c>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="31"/>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C29" s="19" t="s">
+    <row r="29" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="C29" s="20"/>
+      <c r="D29" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="20">
-        <v>5318</v>
-      </c>
-      <c r="L29" s="20">
-        <v>5824</v>
-      </c>
-      <c r="M29" s="20">
-        <v>6065</v>
-      </c>
-      <c r="N29" s="20">
-        <v>6565</v>
-      </c>
-      <c r="O29" s="20">
-        <v>6805</v>
-      </c>
-      <c r="P29" s="20">
-        <v>7105</v>
-      </c>
-      <c r="Q29" s="20">
-        <v>7155</v>
-      </c>
-      <c r="R29" s="20">
-        <v>7355</v>
-      </c>
-      <c r="S29" s="20">
-        <v>7555</v>
-      </c>
-      <c r="T29" s="20">
-        <v>7755</v>
-      </c>
-      <c r="U29" s="20">
-        <v>7955</v>
-      </c>
-      <c r="V29" s="20">
-        <v>8155</v>
-      </c>
-      <c r="W29" s="20">
-        <v>8355</v>
-      </c>
-      <c r="X29" s="20">
-        <v>8555</v>
-      </c>
-      <c r="Y29" s="20">
-        <v>8755</v>
-      </c>
-      <c r="Z29" s="20">
-        <v>8955</v>
-      </c>
-      <c r="AA29" s="20">
-        <v>9155</v>
-      </c>
-      <c r="AB29" s="19"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="19"/>
-      <c r="AF29" s="19"/>
-      <c r="AG29" s="19"/>
-      <c r="AH29" s="19"/>
-      <c r="AI29" s="19"/>
-      <c r="AJ29" s="19"/>
-      <c r="AK29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="35">
+        <v>4740.55</v>
+      </c>
+      <c r="L29" s="35">
+        <v>5044.28125</v>
+      </c>
+      <c r="M29" s="35">
+        <v>5540.25</v>
+      </c>
+      <c r="N29" s="35">
+        <v>5865.5</v>
+      </c>
+      <c r="O29" s="35">
+        <v>6207.875</v>
+      </c>
+      <c r="P29" s="35">
+        <v>6579.75</v>
+      </c>
+      <c r="Q29" s="35">
+        <v>6930.625</v>
+      </c>
+      <c r="R29" s="35">
+        <v>7281.125</v>
+      </c>
+      <c r="S29" s="35">
+        <v>7685.25</v>
+      </c>
+      <c r="T29" s="35">
+        <v>8093.125</v>
+      </c>
+      <c r="U29" s="35">
+        <v>8507.5</v>
+      </c>
+      <c r="V29" s="35">
+        <v>8927.125</v>
+      </c>
+      <c r="W29" s="35">
+        <v>9282</v>
+      </c>
+      <c r="X29" s="35">
+        <v>9591.5</v>
+      </c>
+      <c r="Y29" s="35">
+        <v>9953.25</v>
+      </c>
+      <c r="Z29" s="35">
+        <v>10242.5</v>
+      </c>
+      <c r="AA29" s="35">
+        <v>10550.5</v>
+      </c>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="21"/>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C30" s="19" t="s">
+    <row r="30" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B30" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="C30" s="20"/>
+      <c r="D30" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="20">
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="35">
         <v>25</v>
       </c>
-      <c r="L30" s="20">
+      <c r="L30" s="35">
         <v>25</v>
       </c>
-      <c r="M30" s="20">
+      <c r="M30" s="35">
         <v>25</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="35">
         <v>25</v>
       </c>
-      <c r="O30" s="20">
-        <v>850</v>
-      </c>
-      <c r="P30" s="20">
-        <v>2650</v>
-      </c>
-      <c r="Q30" s="20">
+      <c r="O30" s="35">
+        <v>25</v>
+      </c>
+      <c r="P30" s="35">
+        <v>231.25</v>
+      </c>
+      <c r="Q30" s="35">
+        <v>1525</v>
+      </c>
+      <c r="R30" s="35">
+        <v>2862.5</v>
+      </c>
+      <c r="S30" s="35">
+        <v>3500</v>
+      </c>
+      <c r="T30" s="35">
         <v>4000</v>
       </c>
-      <c r="R30" s="20">
-        <v>5000</v>
-      </c>
-      <c r="S30" s="20">
-        <v>5700</v>
-      </c>
-      <c r="T30" s="20">
-        <v>6500</v>
-      </c>
-      <c r="U30" s="20">
-        <v>7100</v>
-      </c>
-      <c r="V30" s="20">
-        <v>7800</v>
-      </c>
-      <c r="W30" s="20">
-        <v>8500</v>
-      </c>
-      <c r="X30" s="20">
-        <v>9200</v>
-      </c>
-      <c r="Y30" s="20">
-        <v>9900</v>
-      </c>
-      <c r="Z30" s="20">
-        <v>10600</v>
-      </c>
-      <c r="AA30" s="20">
-        <v>11300</v>
-      </c>
-      <c r="AB30" s="19"/>
-      <c r="AC30" s="19"/>
-      <c r="AD30" s="19"/>
-      <c r="AE30" s="19"/>
-      <c r="AF30" s="19"/>
-      <c r="AG30" s="19"/>
-      <c r="AH30" s="19"/>
-      <c r="AI30" s="19"/>
-      <c r="AJ30" s="19"/>
-      <c r="AK30" s="20"/>
+      <c r="U30" s="35">
+        <v>4500</v>
+      </c>
+      <c r="V30" s="35">
+        <v>5175</v>
+      </c>
+      <c r="W30" s="35">
+        <v>5875</v>
+      </c>
+      <c r="X30" s="35">
+        <v>6575</v>
+      </c>
+      <c r="Y30" s="35">
+        <v>7350</v>
+      </c>
+      <c r="Z30" s="35">
+        <v>8350</v>
+      </c>
+      <c r="AA30" s="35">
+        <v>9325</v>
+      </c>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="20"/>
+      <c r="AD30" s="20"/>
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
+      <c r="AG30" s="20"/>
+      <c r="AH30" s="20"/>
+      <c r="AI30" s="20"/>
+      <c r="AJ30" s="20"/>
+      <c r="AK30" s="21"/>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C31" s="19" t="s">
+    <row r="31" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="20"/>
+      <c r="D31" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="20">
-        <v>1194</v>
-      </c>
-      <c r="L31" s="20">
-        <v>2249</v>
-      </c>
-      <c r="M31" s="20">
-        <v>2687</v>
-      </c>
-      <c r="N31" s="20">
-        <v>3575</v>
-      </c>
-      <c r="O31" s="20">
-        <v>4192</v>
-      </c>
-      <c r="P31" s="20">
-        <v>5324</v>
-      </c>
-      <c r="Q31" s="20">
-        <v>6500</v>
-      </c>
-      <c r="R31" s="20">
-        <v>6750</v>
-      </c>
-      <c r="S31" s="20">
-        <v>7050</v>
-      </c>
-      <c r="T31" s="20">
-        <v>7350</v>
-      </c>
-      <c r="U31" s="20">
-        <v>7650</v>
-      </c>
-      <c r="V31" s="20">
-        <v>7950</v>
-      </c>
-      <c r="W31" s="20">
-        <v>8250</v>
-      </c>
-      <c r="X31" s="20">
-        <v>8550</v>
-      </c>
-      <c r="Y31" s="20">
-        <v>8850</v>
-      </c>
-      <c r="Z31" s="20">
-        <v>9150</v>
-      </c>
-      <c r="AA31" s="20">
-        <v>9450</v>
-      </c>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
-      <c r="AE31" s="19"/>
-      <c r="AF31" s="19"/>
-      <c r="AG31" s="19"/>
-      <c r="AH31" s="19"/>
-      <c r="AI31" s="19"/>
-      <c r="AJ31" s="19"/>
-      <c r="AK31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="35">
+        <v>914.93749999999989</v>
+      </c>
+      <c r="L31" s="35">
+        <v>1680.75</v>
+      </c>
+      <c r="M31" s="35">
+        <v>2789.75</v>
+      </c>
+      <c r="N31" s="35">
+        <v>3543.375</v>
+      </c>
+      <c r="O31" s="35">
+        <v>4296.75</v>
+      </c>
+      <c r="P31" s="35">
+        <v>5050.375</v>
+      </c>
+      <c r="Q31" s="35">
+        <v>5805.25</v>
+      </c>
+      <c r="R31" s="35">
+        <v>6505.5</v>
+      </c>
+      <c r="S31" s="35">
+        <v>7105.375</v>
+      </c>
+      <c r="T31" s="35">
+        <v>7695.375</v>
+      </c>
+      <c r="U31" s="35">
+        <v>8277.75</v>
+      </c>
+      <c r="V31" s="35">
+        <v>8857.625</v>
+      </c>
+      <c r="W31" s="35">
+        <v>9402.375</v>
+      </c>
+      <c r="X31" s="35">
+        <v>9880</v>
+      </c>
+      <c r="Y31" s="35">
+        <v>10349.75</v>
+      </c>
+      <c r="Z31" s="35">
+        <v>10812.75</v>
+      </c>
+      <c r="AA31" s="35">
+        <v>11268.5</v>
+      </c>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
+      <c r="AG31" s="20"/>
+      <c r="AH31" s="20"/>
+      <c r="AI31" s="20"/>
+      <c r="AJ31" s="20"/>
+      <c r="AK31" s="21"/>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C32" s="19" t="s">
+    <row r="32" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B32" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="C32" s="20"/>
+      <c r="D32" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="21">
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="35">
         <v>10</v>
       </c>
       <c r="M32" s="22">
@@ -2625,45 +3222,66 @@
       <c r="P32" s="22">
         <v>10</v>
       </c>
-      <c r="Q32" s="21">
+      <c r="Q32" s="35">
         <v>10</v>
       </c>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="19"/>
-      <c r="AC32" s="19"/>
-      <c r="AD32" s="19"/>
-      <c r="AE32" s="19"/>
-      <c r="AF32" s="19"/>
-      <c r="AG32" s="19"/>
-      <c r="AH32" s="19"/>
-      <c r="AI32" s="19"/>
-      <c r="AJ32" s="19"/>
-      <c r="AK32" s="20"/>
+      <c r="R32" s="17">
+        <v>10</v>
+      </c>
+      <c r="S32" s="17">
+        <v>10</v>
+      </c>
+      <c r="T32" s="17">
+        <v>10</v>
+      </c>
+      <c r="U32" s="17">
+        <v>10</v>
+      </c>
+      <c r="V32" s="17">
+        <v>10</v>
+      </c>
+      <c r="W32" s="17">
+        <v>10</v>
+      </c>
+      <c r="X32" s="17">
+        <v>10</v>
+      </c>
+      <c r="Y32" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="17">
+        <v>10</v>
+      </c>
+      <c r="AA32" s="17">
+        <v>10</v>
+      </c>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
+      <c r="AE32" s="20"/>
+      <c r="AF32" s="20"/>
+      <c r="AG32" s="20"/>
+      <c r="AH32" s="20"/>
+      <c r="AI32" s="20"/>
+      <c r="AJ32" s="20"/>
+      <c r="AK32" s="21"/>
     </row>
-    <row r="33" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C33" s="19" t="s">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="C33" s="20"/>
+      <c r="D33" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="21">
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="35">
         <v>12</v>
       </c>
       <c r="M33" s="22">
@@ -2678,332 +3296,439 @@
       <c r="P33" s="22">
         <v>18.400000000000002</v>
       </c>
-      <c r="Q33" s="21">
+      <c r="Q33" s="35">
         <v>20</v>
       </c>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="19"/>
-      <c r="AC33" s="19"/>
-      <c r="AD33" s="19"/>
-      <c r="AE33" s="19"/>
-      <c r="AF33" s="19"/>
-      <c r="AG33" s="19"/>
-      <c r="AH33" s="19"/>
-      <c r="AI33" s="19"/>
-      <c r="AJ33" s="19"/>
-      <c r="AK33" s="20"/>
+      <c r="R33" s="17">
+        <v>20</v>
+      </c>
+      <c r="S33" s="17">
+        <v>20</v>
+      </c>
+      <c r="T33" s="17">
+        <v>20</v>
+      </c>
+      <c r="U33" s="17">
+        <v>20</v>
+      </c>
+      <c r="V33" s="17">
+        <v>20</v>
+      </c>
+      <c r="W33" s="17">
+        <v>20</v>
+      </c>
+      <c r="X33" s="17">
+        <v>20</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>20</v>
+      </c>
+      <c r="Z33" s="17">
+        <v>20</v>
+      </c>
+      <c r="AA33" s="17">
+        <v>20</v>
+      </c>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="20"/>
+      <c r="AG33" s="20"/>
+      <c r="AH33" s="20"/>
+      <c r="AI33" s="20"/>
+      <c r="AJ33" s="20"/>
+      <c r="AK33" s="21"/>
     </row>
-    <row r="34" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C34" s="19" t="s">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B34" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="C34" s="20"/>
+      <c r="D34" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="21">
-        <v>0</v>
-      </c>
-      <c r="M34" s="22">
-        <v>0.86</v>
-      </c>
-      <c r="N34" s="22">
-        <v>1.72</v>
-      </c>
-      <c r="O34" s="22">
-        <v>2.58</v>
-      </c>
-      <c r="P34" s="22">
-        <v>3.44</v>
-      </c>
-      <c r="Q34" s="21">
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="39">
+        <v>0.25</v>
+      </c>
+      <c r="M34" s="39">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="N34" s="39">
+        <v>0.8</v>
+      </c>
+      <c r="O34" s="39">
+        <v>1.45</v>
+      </c>
+      <c r="P34" s="39">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="Q34" s="39">
         <v>4.3</v>
       </c>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="19"/>
-      <c r="Z34" s="19"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="19"/>
-      <c r="AC34" s="19"/>
-      <c r="AD34" s="19"/>
-      <c r="AE34" s="19"/>
-      <c r="AF34" s="19"/>
-      <c r="AG34" s="19"/>
-      <c r="AH34" s="19"/>
-      <c r="AI34" s="19"/>
-      <c r="AJ34" s="19"/>
-      <c r="AK34" s="20"/>
+      <c r="R34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="S34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="T34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="U34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="V34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="W34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="X34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="Y34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="Z34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="AA34" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+      <c r="AE34" s="20"/>
+      <c r="AF34" s="20"/>
+      <c r="AG34" s="20"/>
+      <c r="AH34" s="20"/>
+      <c r="AI34" s="20"/>
+      <c r="AJ34" s="20"/>
+      <c r="AK34" s="21"/>
     </row>
-    <row r="35" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C35" s="19" t="s">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="C35" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="20">
-        <v>2566</v>
-      </c>
-      <c r="F35" s="20">
-        <v>4989</v>
-      </c>
-      <c r="G35" s="20">
-        <v>8264</v>
-      </c>
-      <c r="H35" s="20">
-        <v>12603</v>
-      </c>
-      <c r="I35" s="20">
-        <v>21079</v>
-      </c>
-      <c r="J35" s="20">
-        <v>38679</v>
-      </c>
-      <c r="K35" s="20">
-        <v>60496</v>
-      </c>
-      <c r="L35" s="21">
-        <v>120000</v>
-      </c>
-      <c r="M35" s="22">
-        <v>106000</v>
-      </c>
-      <c r="N35" s="22">
-        <v>92000</v>
-      </c>
-      <c r="O35" s="22">
-        <v>78000</v>
-      </c>
-      <c r="P35" s="22">
-        <v>64000</v>
-      </c>
-      <c r="Q35" s="21">
-        <v>50000</v>
-      </c>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="19"/>
-      <c r="AC35" s="19"/>
-      <c r="AD35" s="19"/>
-      <c r="AE35" s="19"/>
-      <c r="AF35" s="19"/>
-      <c r="AG35" s="19"/>
-      <c r="AH35" s="19"/>
-      <c r="AI35" s="19"/>
-      <c r="AJ35" s="19"/>
-      <c r="AK35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="41">
+        <v>30290</v>
+      </c>
+      <c r="L35" s="35">
+        <v>10808</v>
+      </c>
+      <c r="M35" s="40">
+        <v>25024.6</v>
+      </c>
+      <c r="N35" s="40">
+        <v>39241.199999999997</v>
+      </c>
+      <c r="O35" s="40">
+        <v>53457.799999999996</v>
+      </c>
+      <c r="P35" s="40">
+        <v>67674.399999999994</v>
+      </c>
+      <c r="Q35" s="35">
+        <v>81891</v>
+      </c>
+      <c r="R35" s="40">
+        <v>100657.8</v>
+      </c>
+      <c r="S35" s="40">
+        <v>119424.6</v>
+      </c>
+      <c r="T35" s="40">
+        <v>138191.4</v>
+      </c>
+      <c r="U35" s="40">
+        <v>156958.19999999998</v>
+      </c>
+      <c r="V35" s="40">
+        <v>175724.99999999997</v>
+      </c>
+      <c r="W35" s="40">
+        <v>194491.79999999996</v>
+      </c>
+      <c r="X35" s="40">
+        <v>213258.59999999995</v>
+      </c>
+      <c r="Y35" s="40">
+        <v>232025.39999999994</v>
+      </c>
+      <c r="Z35" s="40">
+        <v>250792.19999999992</v>
+      </c>
+      <c r="AA35" s="35">
+        <v>269559</v>
+      </c>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
+      <c r="AE35" s="20"/>
+      <c r="AF35" s="20"/>
+      <c r="AG35" s="20"/>
+      <c r="AH35" s="20"/>
+      <c r="AI35" s="20"/>
+      <c r="AJ35" s="20"/>
+      <c r="AK35" s="21"/>
     </row>
-    <row r="36" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C36" s="19" t="s">
+    <row r="36" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="C36" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="E36" s="20">
-        <v>229</v>
-      </c>
-      <c r="F36" s="20">
-        <v>1358</v>
-      </c>
-      <c r="G36" s="20">
-        <v>2813</v>
-      </c>
-      <c r="H36" s="20">
-        <v>4784</v>
-      </c>
-      <c r="I36" s="20">
-        <v>7056</v>
-      </c>
-      <c r="J36" s="20">
-        <v>10823</v>
-      </c>
-      <c r="K36" s="20">
-        <v>14423</v>
-      </c>
-      <c r="L36" s="20">
-        <v>18770</v>
-      </c>
-      <c r="M36" s="22">
-        <v>43616</v>
-      </c>
-      <c r="N36" s="22">
-        <v>68462</v>
-      </c>
-      <c r="O36" s="22">
-        <v>93308</v>
-      </c>
-      <c r="P36" s="22">
-        <v>118154</v>
-      </c>
-      <c r="Q36" s="21">
-        <v>143000</v>
-      </c>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="19"/>
-      <c r="W36" s="19"/>
-      <c r="X36" s="19"/>
-      <c r="Y36" s="19"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="19"/>
-      <c r="AC36" s="19"/>
-      <c r="AD36" s="19"/>
-      <c r="AE36" s="19"/>
-      <c r="AF36" s="19"/>
-      <c r="AG36" s="19"/>
-      <c r="AH36" s="19"/>
-      <c r="AI36" s="19"/>
-      <c r="AJ36" s="19"/>
-      <c r="AK36" s="20"/>
+      <c r="K36" s="35">
+        <v>22594</v>
+      </c>
+      <c r="L36" s="35">
+        <v>31445.340470809999</v>
+      </c>
+      <c r="M36" s="35">
+        <v>53015.009948920997</v>
+      </c>
+      <c r="N36" s="35">
+        <v>74768.033133266013</v>
+      </c>
+      <c r="O36" s="35">
+        <v>97085.80137452601</v>
+      </c>
+      <c r="P36" s="35">
+        <v>119719.602917269</v>
+      </c>
+      <c r="Q36" s="35">
+        <v>142350.36580480903</v>
+      </c>
+      <c r="R36" s="35">
+        <v>165081.94181390601</v>
+      </c>
+      <c r="S36" s="35">
+        <v>187346.88963736803</v>
+      </c>
+      <c r="T36" s="35">
+        <v>210029.48462770402</v>
+      </c>
+      <c r="U36" s="35">
+        <v>232675.82927241101</v>
+      </c>
+      <c r="V36" s="35">
+        <v>254838.99066632299</v>
+      </c>
+      <c r="W36" s="35">
+        <v>277005.17211469699</v>
+      </c>
+      <c r="X36" s="35">
+        <v>299162.26804125699</v>
+      </c>
+      <c r="Y36" s="35">
+        <v>321719.28957132105</v>
+      </c>
+      <c r="Z36" s="35">
+        <v>338758.85337760701</v>
+      </c>
+      <c r="AA36" s="35">
+        <v>407140.970632207</v>
+      </c>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="20"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
+      <c r="AG36" s="20"/>
+      <c r="AH36" s="20"/>
+      <c r="AI36" s="20"/>
+      <c r="AJ36" s="20"/>
+      <c r="AK36" s="21"/>
     </row>
-    <row r="37" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C37" s="19" t="s">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B37" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="C37" s="20"/>
+      <c r="D37" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="21">
-        <v>0</v>
-      </c>
-      <c r="M37" s="40">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="N37" s="40">
-        <v>2.5600000000000001E-2</v>
-      </c>
-      <c r="O37" s="40">
-        <v>3.8400000000000004E-2</v>
-      </c>
-      <c r="P37" s="40">
-        <v>5.1200000000000002E-2</v>
-      </c>
-      <c r="Q37" s="41">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="19"/>
-      <c r="X37" s="19"/>
-      <c r="Y37" s="19"/>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="19"/>
-      <c r="AC37" s="19"/>
-      <c r="AD37" s="19"/>
-      <c r="AE37" s="19"/>
-      <c r="AF37" s="19"/>
-      <c r="AG37" s="19"/>
-      <c r="AH37" s="19"/>
-      <c r="AI37" s="19"/>
-      <c r="AJ37" s="19"/>
-      <c r="AK37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="J37" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="K37" s="38">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="L37" s="38">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="M37" s="38">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="N37" s="38">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="O37" s="38">
+        <v>1.5754000000000001E-2</v>
+      </c>
+      <c r="P37" s="38">
+        <v>3.0107999999999999E-2</v>
+      </c>
+      <c r="Q37" s="38">
+        <v>4.4462000000000002E-2</v>
+      </c>
+      <c r="R37" s="38">
+        <v>9.401580000000001E-2</v>
+      </c>
+      <c r="S37" s="38">
+        <v>0.14356960000000002</v>
+      </c>
+      <c r="T37" s="38">
+        <v>0.1931234</v>
+      </c>
+      <c r="U37" s="38">
+        <v>0.24267720000000001</v>
+      </c>
+      <c r="V37" s="38">
+        <v>0.29223100000000002</v>
+      </c>
+      <c r="W37" s="38">
+        <v>0.3417848</v>
+      </c>
+      <c r="X37" s="38">
+        <v>0.39133860000000004</v>
+      </c>
+      <c r="Y37" s="38">
+        <v>0.44089240000000002</v>
+      </c>
+      <c r="Z37" s="38">
+        <v>0.4904462</v>
+      </c>
+      <c r="AA37" s="38">
+        <v>0.54</v>
+      </c>
+      <c r="AB37" s="20"/>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="20"/>
+      <c r="AE37" s="20"/>
+      <c r="AF37" s="20"/>
+      <c r="AG37" s="20"/>
+      <c r="AH37" s="20"/>
+      <c r="AI37" s="20"/>
+      <c r="AJ37" s="20"/>
+      <c r="AK37" s="21"/>
     </row>
-    <row r="38" spans="3:37" x14ac:dyDescent="0.25">
-      <c r="C38" s="19" t="s">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="C38" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="42">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="J38" s="22">
-        <v>5.875E-3</v>
-      </c>
-      <c r="K38" s="22">
-        <v>7.2500000000000004E-3</v>
-      </c>
-      <c r="L38" s="22">
-        <v>8.6250000000000007E-3</v>
-      </c>
-      <c r="M38" s="21">
-        <v>0.01</v>
-      </c>
-      <c r="N38" s="22">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="O38" s="22">
-        <v>7.9999999999999988E-2</v>
-      </c>
-      <c r="P38" s="22">
-        <v>0.11499999999999999</v>
-      </c>
-      <c r="Q38" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="19"/>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="19"/>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="19"/>
-      <c r="AC38" s="19"/>
-      <c r="AD38" s="19"/>
-      <c r="AE38" s="19"/>
-      <c r="AF38" s="19"/>
-      <c r="AG38" s="19"/>
-      <c r="AH38" s="19"/>
-      <c r="AI38" s="19"/>
-      <c r="AJ38" s="19"/>
-      <c r="AK38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="38">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="J38" s="38">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="K38" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="L38" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="M38" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="N38" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="O38" s="38">
+        <v>6.3015999999999989E-2</v>
+      </c>
+      <c r="P38" s="38">
+        <v>0.12043199999999998</v>
+      </c>
+      <c r="Q38" s="38">
+        <v>0.17784800000000001</v>
+      </c>
+      <c r="R38" s="38">
+        <v>0.37606319999999999</v>
+      </c>
+      <c r="S38" s="38">
+        <v>0.57427839999999997</v>
+      </c>
+      <c r="T38" s="38">
+        <v>0.7724936</v>
+      </c>
+      <c r="U38" s="38">
+        <v>0.97070879999999993</v>
+      </c>
+      <c r="V38" s="38">
+        <v>1.1689240000000001</v>
+      </c>
+      <c r="W38" s="38">
+        <v>1.3671392</v>
+      </c>
+      <c r="X38" s="38">
+        <v>1.5653543999999999</v>
+      </c>
+      <c r="Y38" s="38">
+        <v>1.7635695999999998</v>
+      </c>
+      <c r="Z38" s="38">
+        <v>1.9617848</v>
+      </c>
+      <c r="AA38" s="38">
+        <v>2.16</v>
+      </c>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="20"/>
+      <c r="AE38" s="20"/>
+      <c r="AF38" s="20"/>
+      <c r="AG38" s="20"/>
+      <c r="AH38" s="20"/>
+      <c r="AI38" s="20"/>
+      <c r="AJ38" s="20"/>
+      <c r="AK38" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>
-  <conditionalFormatting sqref="P6:AO6 P7:AN13">
+  <conditionalFormatting sqref="Q6:AO6 P6:P13 Q7:AN13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>0.000000000001</formula>
       <formula>0.001</formula>
